--- a/output/pdf_financials_xlsx/GRGD.xlsx
+++ b/output/pdf_financials_xlsx/GRGD.xlsx
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>74.19499999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>82.47799999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>74.19499999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>82.47799999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1157,10 +1157,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>103.623</v>
+        <v>29.428</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>133.921</v>
+        <v>51.443</v>
       </c>
     </row>
     <row r="49">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRGD.xlsx
+++ b/output/pdf_financials_xlsx/GRGD.xlsx
@@ -3430,7 +3430,11 @@
           <t>Additions to intangible assets 13</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>-10.648</v>
       </c>

--- a/output/pdf_financials_xlsx/GRGD.xlsx
+++ b/output/pdf_financials_xlsx/GRGD.xlsx
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>19.466</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>24.321</v>
       </c>
     </row>
     <row r="65">
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>30.438</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>56.921</v>
       </c>
     </row>
     <row r="68">
@@ -2081,15 +2081,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>46.693</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>-85.52</v>
       </c>
     </row>
     <row r="120">
@@ -2297,15 +2293,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>174.315</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>344.868</v>
       </c>
     </row>
   </sheetData>
@@ -3378,7 +3370,11 @@
           <t>Cash generated from operating activities</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E39" s="5" t="n">
         <v>226.974</v>
       </c>
